--- a/data/trans_bre/P38B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,56</t>
+          <t>2,56; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,29</t>
+          <t>1,73; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,1</t>
+          <t>1,4; 8,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,75</t>
+          <t>2,88; 8,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,45</t>
+          <t>1,92; 8,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,41</t>
+          <t>1,53; 9,44</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,0</t>
+          <t>3,77; 8,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,48</t>
+          <t>3,64; 8,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 37,25</t>
+          <t>2,19; 33,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,74</t>
+          <t>4,76; 11,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,93</t>
+          <t>4,48; 10,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 80,37</t>
+          <t>2,81; 65,13</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 3,79</t>
+          <t>-5,75; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 7,05</t>
+          <t>-2,87; 6,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,9</t>
+          <t>1,64; 10,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 4,5</t>
+          <t>-6,45; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,85</t>
+          <t>-3,41; 8,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 15,27</t>
+          <t>1,92; 13,38</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,45</t>
+          <t>3,92; 7,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,23</t>
+          <t>3,94; 7,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 30,77</t>
+          <t>4,44; 27,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,17</t>
+          <t>4,71; 9,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,93</t>
+          <t>4,73; 9,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 53,64</t>
+          <t>5,5; 45,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,45</t>
+          <t>2,41; 7,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,98</t>
+          <t>1,58; 7,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,21</t>
+          <t>3,64; 10,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,65</t>
+          <t>2,68; 8,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,01</t>
+          <t>1,74; 8,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,44</t>
+          <t>4,04; 12,58</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,8</t>
+          <t>3,77; 9,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,49</t>
+          <t>3,67; 8,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 33,68</t>
+          <t>3,01; 8,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,5</t>
+          <t>4,81; 11,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,86</t>
+          <t>4,54; 10,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 65,13</t>
+          <t>3,82; 11,94</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,59</t>
+          <t>-5,55; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,49</t>
+          <t>-2,27; 6,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,57</t>
+          <t>1,49; 9,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 4,21</t>
+          <t>-6,19; 4,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 8,11</t>
+          <t>-2,68; 8,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,38</t>
+          <t>1,69; 11,63</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,59</t>
+          <t>4,04; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,39</t>
+          <t>3,9; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 27,13</t>
+          <t>4,67; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,4</t>
+          <t>4,84; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,13</t>
+          <t>4,72; 9,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 45,89</t>
+          <t>5,77; 11,2</t>
         </is>
       </c>
     </row>
